--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="270">
   <si>
     <t/>
   </si>
@@ -397,421 +397,430 @@
     <t>DETTOL ASPTC WPS10'S</t>
   </si>
   <si>
+    <t>20141960</t>
+  </si>
+  <si>
+    <t>CHARM SFNGHT PNTS 2S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20133707</t>
+  </si>
+  <si>
+    <t>CHARM SP.PANT L-XL2S</t>
+  </si>
+  <si>
+    <t>20092849</t>
+  </si>
+  <si>
+    <t>SFTX CLN MENST M-L2S</t>
+  </si>
+  <si>
+    <t>20136913</t>
+  </si>
+  <si>
+    <t>SFTX CLN MENST M-L5S</t>
+  </si>
+  <si>
+    <t>20121204</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 30/29</t>
+  </si>
+  <si>
+    <t>20045293</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NGH 8/30</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20021323</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 6/35</t>
+  </si>
+  <si>
+    <t>10036092</t>
+  </si>
+  <si>
+    <t>LAURIER RN WG 8'S/35</t>
+  </si>
+  <si>
+    <t>20135430</t>
+  </si>
+  <si>
+    <t>LAURIER RN 18'S 35CM</t>
+  </si>
+  <si>
+    <t>20048563</t>
+  </si>
+  <si>
+    <t>LAURIER R/N 8'S 40CM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20114105</t>
+  </si>
+  <si>
+    <t>CHRM CL.FRSH 6S 42CM</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20099396</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH NW 8'S</t>
+  </si>
+  <si>
+    <t>20098616</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH NW 10S</t>
+  </si>
+  <si>
+    <t>20091792</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH WG 15S</t>
+  </si>
+  <si>
+    <t>20091786</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH NW 17S</t>
+  </si>
+  <si>
+    <t>20130850</t>
+  </si>
+  <si>
+    <t>CHRM COOL.FRSH WG14S</t>
+  </si>
+  <si>
+    <t>20140121</t>
+  </si>
+  <si>
+    <t>SOFTX BR.COOL 23-14S</t>
+  </si>
+  <si>
+    <t>20017043</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 7/42</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20121205</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 18/35</t>
+  </si>
+  <si>
+    <t>20047284</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 12/35</t>
+  </si>
+  <si>
+    <t>10032895</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT GW 11/35</t>
+  </si>
+  <si>
+    <t>10005974</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 9S/29</t>
+  </si>
+  <si>
+    <t>20140120</t>
+  </si>
+  <si>
+    <t>SOFTX BRY COOL 36-8S</t>
+  </si>
+  <si>
+    <t>20113228</t>
+  </si>
+  <si>
+    <t>SOFTEX DS 3IN1 16'S</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20139608</t>
+  </si>
+  <si>
+    <t>LAURIER RLX 30CM 24S</t>
+  </si>
+  <si>
+    <t>20021326</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 16/30</t>
+  </si>
+  <si>
+    <t>20021324</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 12/35</t>
+  </si>
+  <si>
+    <t>20136041</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 14/42</t>
+  </si>
+  <si>
+    <t>10010189</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 18/29</t>
+  </si>
+  <si>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20115506</t>
+  </si>
+  <si>
+    <t>IDM TISU BMB ROL 4'S</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>20029296</t>
+  </si>
+  <si>
+    <t>IDM WET TISSUE 10'S</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20141206</t>
+  </si>
+  <si>
+    <t>LARISST M.W WIPE 8X8</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>20124826</t>
+  </si>
+  <si>
+    <t>FAVOUR TISU WJH 120S</t>
+  </si>
+  <si>
+    <t>20103297</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP200</t>
+  </si>
+  <si>
+    <t>20133704</t>
+  </si>
+  <si>
+    <t>IDM BB.FCL TISSU 70S</t>
+  </si>
+  <si>
+    <t>20141207</t>
+  </si>
+  <si>
+    <t>WATERU WHT BMBOO 50S</t>
+  </si>
+  <si>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20045887</t>
+  </si>
+  <si>
+    <t>IDM TISU DP/HND 150S</t>
+  </si>
+  <si>
+    <t>10038692</t>
+  </si>
+  <si>
+    <t>MULTI TIS.NON.PERPUM</t>
+  </si>
+  <si>
+    <t>20122914</t>
+  </si>
+  <si>
+    <t>FAVOUR CH FC TIS200S</t>
+  </si>
+  <si>
+    <t>20020128</t>
+  </si>
+  <si>
+    <t>NICE FC/TISUE NP250S</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20026897</t>
+  </si>
+  <si>
+    <t>TESSA FAC.TISSUE 260</t>
+  </si>
+  <si>
+    <t>20034036</t>
+  </si>
+  <si>
+    <t>PASEO SMART 540PLY</t>
+  </si>
+  <si>
+    <t>10005468</t>
+  </si>
+  <si>
+    <t>PASEO FC.SOFT 510PLY</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20113083</t>
+  </si>
+  <si>
+    <t>TESSA FC.TISU 2X200S</t>
+  </si>
+  <si>
+    <t>10014168</t>
+  </si>
+  <si>
+    <t>NICE BUY1FREE1 2X200</t>
+  </si>
+  <si>
+    <t>20128974</t>
+  </si>
+  <si>
+    <t>MONTISS FC TISUE200S</t>
+  </si>
+  <si>
+    <t>20035998</t>
+  </si>
+  <si>
+    <t>INDOMRET TRVL PACK50</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20006422</t>
+  </si>
+  <si>
+    <t>TESSA FAC.LOONEY TP9</t>
+  </si>
+  <si>
+    <t>20001221</t>
+  </si>
+  <si>
+    <t>PASEO TRVL.PC TISSUE</t>
+  </si>
+  <si>
+    <t>20063288</t>
+  </si>
+  <si>
+    <t>PASEO PURE SOFT 130S</t>
+  </si>
+  <si>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
+  </si>
+  <si>
+    <t>20115171</t>
+  </si>
+  <si>
+    <t>IDM TISU BAMBU 150'S</t>
+  </si>
+  <si>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20115364</t>
   </si>
   <si>
     <t>CHARM SP PANTIES 2S</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20133707</t>
-  </si>
-  <si>
-    <t>CHARM SP.PANT L-XL2S</t>
-  </si>
-  <si>
-    <t>20092849</t>
-  </si>
-  <si>
-    <t>SFTX CLN MENST M-L2S</t>
-  </si>
-  <si>
-    <t>20136913</t>
-  </si>
-  <si>
-    <t>SFTX CLN MENST M-L5S</t>
-  </si>
-  <si>
-    <t>20121204</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 30/29</t>
-  </si>
-  <si>
-    <t>20045293</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NGH 8/30</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20021323</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 6/35</t>
-  </si>
-  <si>
-    <t>10036092</t>
-  </si>
-  <si>
-    <t>LAURIER RN WG 8'S/35</t>
-  </si>
-  <si>
-    <t>20135430</t>
-  </si>
-  <si>
-    <t>LAURIER RN 18'S 35CM</t>
-  </si>
-  <si>
-    <t>20048563</t>
-  </si>
-  <si>
-    <t>LAURIER R/N 8'S 40CM</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20114105</t>
-  </si>
-  <si>
-    <t>CHRM CL.FRSH 6S 42CM</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20099396</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH NW 8'S</t>
-  </si>
-  <si>
-    <t>20098616</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH NW 10S</t>
-  </si>
-  <si>
-    <t>20091792</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH WG 15S</t>
-  </si>
-  <si>
-    <t>20091786</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH NW 17S</t>
-  </si>
-  <si>
-    <t>20130850</t>
-  </si>
-  <si>
-    <t>CHRM COOL.FRSH WG14S</t>
-  </si>
-  <si>
-    <t>20140121</t>
-  </si>
-  <si>
-    <t>SOFTX BR.COOL 23-14S</t>
-  </si>
-  <si>
-    <t>20017043</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 7/42</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20121205</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 18/35</t>
-  </si>
-  <si>
-    <t>20047284</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 12/35</t>
-  </si>
-  <si>
-    <t>10032895</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT GW 11/35</t>
-  </si>
-  <si>
-    <t>10005974</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 9S/29</t>
-  </si>
-  <si>
-    <t>20140120</t>
-  </si>
-  <si>
-    <t>SOFTX BRY COOL 36-8S</t>
-  </si>
-  <si>
-    <t>20113228</t>
-  </si>
-  <si>
-    <t>SOFTEX DS 3IN1 16'S</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20139608</t>
-  </si>
-  <si>
-    <t>LAURIER RLX 30CM 24S</t>
-  </si>
-  <si>
-    <t>20021326</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 16/30</t>
-  </si>
-  <si>
-    <t>20021324</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 12/35</t>
-  </si>
-  <si>
-    <t>20136041</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 14/42</t>
-  </si>
-  <si>
-    <t>10010189</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 18/29</t>
-  </si>
-  <si>
-    <t>20140802</t>
-  </si>
-  <si>
-    <t>IDM TISU DAPUR 1+1</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20115506</t>
-  </si>
-  <si>
-    <t>IDM TISU BMB ROL 4'S</t>
-  </si>
-  <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
-  </si>
-  <si>
-    <t>20029296</t>
-  </si>
-  <si>
-    <t>IDM WET TISSUE 10'S</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20141206</t>
-  </si>
-  <si>
-    <t>LARISST M.W WIPE 8X8</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>20124826</t>
-  </si>
-  <si>
-    <t>FAVOUR TISU WJH 120S</t>
-  </si>
-  <si>
-    <t>20103297</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP200</t>
-  </si>
-  <si>
-    <t>20133704</t>
-  </si>
-  <si>
-    <t>IDM BB.FCL TISSU 70S</t>
-  </si>
-  <si>
-    <t>20141207</t>
-  </si>
-  <si>
-    <t>WATERU WHT BMBOO 50S</t>
-  </si>
-  <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20045887</t>
-  </si>
-  <si>
-    <t>IDM TISU DP/HND 150S</t>
-  </si>
-  <si>
-    <t>10038692</t>
-  </si>
-  <si>
-    <t>MULTI TIS.NON.PERPUM</t>
-  </si>
-  <si>
-    <t>20122914</t>
-  </si>
-  <si>
-    <t>FAVOUR CH FC TIS200S</t>
-  </si>
-  <si>
-    <t>20020128</t>
-  </si>
-  <si>
-    <t>NICE FC/TISUE NP250S</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20026897</t>
-  </si>
-  <si>
-    <t>TESSA FAC.TISSUE 260</t>
-  </si>
-  <si>
-    <t>20034036</t>
-  </si>
-  <si>
-    <t>PASEO SMART 540PLY</t>
-  </si>
-  <si>
-    <t>10005468</t>
-  </si>
-  <si>
-    <t>PASEO FC.SOFT 510PLY</t>
-  </si>
-  <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20113083</t>
-  </si>
-  <si>
-    <t>TESSA FC.TISU 2X200S</t>
-  </si>
-  <si>
-    <t>10014168</t>
-  </si>
-  <si>
-    <t>NICE BUY1FREE1 2X200</t>
-  </si>
-  <si>
-    <t>20128974</t>
-  </si>
-  <si>
-    <t>MONTISS FC TISUE200S</t>
-  </si>
-  <si>
-    <t>20035998</t>
-  </si>
-  <si>
-    <t>INDOMRET TRVL PACK50</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20006422</t>
-  </si>
-  <si>
-    <t>TESSA FAC.LOONEY TP9</t>
-  </si>
-  <si>
-    <t>20001221</t>
-  </si>
-  <si>
-    <t>PASEO TRVL.PC TISSUE</t>
-  </si>
-  <si>
-    <t>20063288</t>
-  </si>
-  <si>
-    <t>PASEO PURE SOFT 130S</t>
-  </si>
-  <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>20115171</t>
-  </si>
-  <si>
-    <t>IDM TISU BAMBU 150'S</t>
-  </si>
-  <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>999</t>
   </si>
 </sst>
 </file>
@@ -1204,13 +1213,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -2352,7 +2361,7 @@
         <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3529,7 +3538,7 @@
         <v>261</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3549,7 +3558,7 @@
         <v>261</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3569,10 +3578,30 @@
         <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>266</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="267">
   <si>
     <t/>
   </si>
@@ -812,15 +812,6 @@
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20115364</t>
-  </si>
-  <si>
-    <t>CHARM SP PANTIES 2S</t>
-  </si>
-  <si>
-    <t>999</t>
   </si>
 </sst>
 </file>
@@ -1213,13 +1204,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -3584,26 +3575,6 @@
         <v>266</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="265">
   <si>
     <t/>
   </si>
@@ -610,19 +610,13 @@
     <t>IDM TISU ROL 8'S</t>
   </si>
   <si>
-    <t>20029296</t>
-  </si>
-  <si>
-    <t>IDM WET TISSUE 10'S</t>
+    <t>20141206</t>
+  </si>
+  <si>
+    <t>LARISST M.W WIPE 8X8</t>
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>20141206</t>
-  </si>
-  <si>
-    <t>LARISST M.W WIPE 8X8</t>
   </si>
   <si>
     <t>20140679</t>
@@ -1204,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2989,10 +2983,10 @@
         <v>201</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3009,7 +3003,7 @@
         <v>201</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>12</v>
@@ -3029,7 +3023,7 @@
         <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>12</v>
@@ -3049,10 +3043,10 @@
         <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3069,7 +3063,7 @@
         <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3089,10 +3083,10 @@
         <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3106,30 +3100,30 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3146,13 +3140,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3166,10 +3160,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>12</v>
@@ -3186,10 +3180,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>12</v>
@@ -3197,19 +3191,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>12</v>
@@ -3226,10 +3220,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>12</v>
@@ -3246,10 +3240,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>12</v>
@@ -3266,33 +3260,33 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3306,10 +3300,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>12</v>
@@ -3326,10 +3320,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>12</v>
@@ -3346,33 +3340,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3386,10 +3380,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>12</v>
@@ -3406,10 +3400,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>12</v>
@@ -3426,30 +3420,30 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3466,13 +3460,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3486,13 +3480,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3506,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3517,19 +3511,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3546,33 +3540,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="268">
   <si>
     <t/>
   </si>
@@ -647,6 +647,15 @@
   </si>
   <si>
     <t>WATERU WHT BMBOO 50S</t>
+  </si>
+  <si>
+    <t>20142611</t>
+  </si>
+  <si>
+    <t>IDM ALCHOL WIPE2X10S</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
   </si>
   <si>
     <t>20098520</t>
@@ -1198,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2983,7 +2992,7 @@
         <v>201</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>12</v>
@@ -3003,7 +3012,7 @@
         <v>201</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>12</v>
@@ -3023,7 +3032,7 @@
         <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>12</v>
@@ -3043,7 +3052,7 @@
         <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3063,7 +3072,7 @@
         <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3083,7 +3092,7 @@
         <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>150</v>
@@ -3100,13 +3109,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3120,10 +3129,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3131,39 +3140,39 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>12</v>
@@ -3171,19 +3180,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>12</v>
@@ -3200,10 +3209,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>12</v>
@@ -3211,19 +3220,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>12</v>
@@ -3231,19 +3240,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>12</v>
@@ -3251,22 +3260,22 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,30 +3289,30 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>12</v>
@@ -3311,19 +3320,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>12</v>
@@ -3331,22 +3340,22 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3360,30 +3369,30 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>12</v>
@@ -3391,19 +3400,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>12</v>
@@ -3411,22 +3420,22 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3440,10 +3449,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3451,59 +3460,59 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3520,10 +3529,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3531,22 +3540,42 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F117" s="1" t="s">
-        <v>264</v>
+      <c r="F118" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -1695,7 +1695,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1715,7 +1715,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -196,13 +196,13 @@
     <t>20140429</t>
   </si>
   <si>
-    <t>CHARM NIGHT DS 17/29</t>
+    <t>CHARM N DS 17 29 CM</t>
   </si>
   <si>
     <t>20140420</t>
   </si>
   <si>
-    <t>CHARM NGHT DS 11S/35</t>
+    <t>CHARM N DS 11S 35 CM</t>
   </si>
   <si>
     <t>20130843</t>
@@ -529,7 +529,7 @@
     <t>20047284</t>
   </si>
   <si>
-    <t>CHARM NIGHT WG 12/35</t>
+    <t>CHARM N WG 12 35 CM</t>
   </si>
   <si>
     <t>10032895</t>
@@ -742,7 +742,7 @@
     <t>20035998</t>
   </si>
   <si>
-    <t>INDOMRET TRVL PACK50</t>
+    <t>IDM TRVL PACK 50'S</t>
   </si>
   <si>
     <t>20</t>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -196,13 +196,13 @@
     <t>20140429</t>
   </si>
   <si>
-    <t>CHARM N DS 17 29 CM</t>
+    <t>CHARM NIGHT DS 17/29</t>
   </si>
   <si>
     <t>20140420</t>
   </si>
   <si>
-    <t>CHARM N DS 11S 35 CM</t>
+    <t>CHARM NGHT DS 11S/35</t>
   </si>
   <si>
     <t>20130843</t>
@@ -529,7 +529,7 @@
     <t>20047284</t>
   </si>
   <si>
-    <t>CHARM N WG 12 35 CM</t>
+    <t>CHARM NIGHT WG 12/35</t>
   </si>
   <si>
     <t>10032895</t>
@@ -742,7 +742,7 @@
     <t>20035998</t>
   </si>
   <si>
-    <t>IDM TRVL PACK 50'S</t>
+    <t>INDOMRET TRVL PACK50</t>
   </si>
   <si>
     <t>20</t>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -613,7 +613,7 @@
     <t>20141206</t>
   </si>
   <si>
-    <t>LARISST M.W WIPE 8X8</t>
+    <t>LARISST MN PCK 8X8'S</t>
   </si>
   <si>
     <t>16</t>
@@ -2992,7 +2992,7 @@
         <v>201</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>12</v>
@@ -3012,7 +3012,7 @@
         <v>201</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>12</v>
@@ -3032,7 +3032,7 @@
         <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>12</v>
@@ -3052,7 +3052,7 @@
         <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3072,7 +3072,7 @@
         <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3092,7 +3092,7 @@
         <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>150</v>
@@ -3112,7 +3112,7 @@
         <v>201</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>214</v>
